--- a/용량.xlsx
+++ b/용량.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISH\Desktop\ADC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A2D233-D832-4B5B-AC77-A30DC6F4F752}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F008DD14-AD0F-47CE-83A1-931B1ECD152A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{B184FB45-8F2A-4F7C-BB60-869406843071}"/>
   </bookViews>
@@ -296,10 +296,6 @@
   </si>
   <si>
     <t>0.94g q24h</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.94g q8h</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1053,6 +1049,10 @@
   </si>
   <si>
     <t>Load ^6~12mg/kg q12h x 3, 이후 q72h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.94g q48h</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1482,7 +1482,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>200</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>34</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B40">
         <v>30</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B44">
         <v>-1</v>
@@ -2354,7 +2354,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B45">
         <v>-2</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B46">
         <v>50</v>
@@ -2394,15 +2394,15 @@
         <v>6</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B47">
         <v>30</v>
@@ -2414,15 +2414,15 @@
         <v>61</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B48">
         <v>15</v>
@@ -2431,18 +2431,18 @@
         <v>30</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2451,18 +2451,18 @@
         <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B50">
         <v>-1</v>
@@ -2474,15 +2474,15 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51">
         <v>-2</v>
@@ -2494,15 +2494,15 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B52">
         <v>120</v>
@@ -2511,18 +2511,18 @@
         <v>200</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" t="s">
         <v>80</v>
       </c>
-      <c r="E52" t="s">
-        <v>81</v>
-      </c>
       <c r="F52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B53">
         <v>60</v>
@@ -2531,18 +2531,18 @@
         <v>120</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
         <v>37</v>
       </c>
       <c r="F53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54">
         <v>30</v>
@@ -2554,15 +2554,15 @@
         <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55">
         <v>15</v>
@@ -2571,18 +2571,18 @@
         <v>30</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
       </c>
       <c r="F55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -2591,18 +2591,18 @@
         <v>15</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57">
         <v>-1</v>
@@ -2614,15 +2614,15 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B58">
         <v>-2</v>
@@ -2634,15 +2634,15 @@
         <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B59">
         <v>30</v>
@@ -2657,12 +2657,12 @@
         <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -2671,18 +2671,18 @@
         <v>30</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B61">
         <v>-1</v>
@@ -2694,15 +2694,15 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62">
         <v>-2</v>
@@ -2717,12 +2717,12 @@
         <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B63">
         <v>90</v>
@@ -2731,18 +2731,18 @@
         <v>200</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64">
         <v>60</v>
@@ -2751,18 +2751,18 @@
         <v>90</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B65">
         <v>30</v>
@@ -2774,15 +2774,15 @@
         <v>57</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66">
         <v>15</v>
@@ -2791,18 +2791,18 @@
         <v>30</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B67">
         <v>-1</v>
@@ -2814,15 +2814,15 @@
         <v>14</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B68">
         <v>-2</v>
@@ -2834,10 +2834,10 @@
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2962,7 +2962,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B75">
         <v>-2</v>
@@ -2971,18 +2971,18 @@
         <v>200</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E75" t="s">
         <v>97</v>
       </c>
-      <c r="E75" t="s">
-        <v>98</v>
-      </c>
       <c r="F75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B76">
         <v>50</v>
@@ -2994,15 +2994,15 @@
         <v>6</v>
       </c>
       <c r="E76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B77">
         <v>30</v>
@@ -3014,15 +3014,15 @@
         <v>61</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78">
         <v>10</v>
@@ -3034,15 +3034,15 @@
         <v>25</v>
       </c>
       <c r="E78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B79">
         <v>-1</v>
@@ -3054,15 +3054,15 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B80">
         <v>-2</v>
@@ -3074,15 +3074,15 @@
         <v>15</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F80" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B81">
         <v>30</v>
@@ -3091,18 +3091,18 @@
         <v>200</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E81" t="s">
         <v>107</v>
       </c>
-      <c r="E81" t="s">
-        <v>108</v>
-      </c>
       <c r="F81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B82">
         <v>15</v>
@@ -3111,18 +3111,18 @@
         <v>30</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B83">
         <v>5</v>
@@ -3131,18 +3131,18 @@
         <v>15</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B84">
         <v>-1</v>
@@ -3154,15 +3154,15 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B85">
         <v>-2</v>
@@ -3174,15 +3174,15 @@
         <v>15</v>
       </c>
       <c r="E85" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B86">
         <v>90</v>
@@ -3191,18 +3191,18 @@
         <v>200</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F86" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B87">
         <v>60</v>
@@ -3211,18 +3211,18 @@
         <v>90</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B88">
         <v>30</v>
@@ -3234,15 +3234,15 @@
         <v>57</v>
       </c>
       <c r="E88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B89">
         <v>15</v>
@@ -3251,18 +3251,18 @@
         <v>30</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -3271,18 +3271,18 @@
         <v>15</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E90" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F90" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B91">
         <v>-1</v>
@@ -3294,15 +3294,15 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F91" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B92">
         <v>-2</v>
@@ -3314,15 +3314,15 @@
         <v>15</v>
       </c>
       <c r="E92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B93">
         <v>30</v>
@@ -3331,18 +3331,18 @@
         <v>200</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E93" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B94">
         <v>10</v>
@@ -3351,18 +3351,18 @@
         <v>30</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E94" t="s">
         <v>122</v>
       </c>
-      <c r="E94" t="s">
-        <v>123</v>
-      </c>
       <c r="F94" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -3374,15 +3374,15 @@
         <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96">
         <v>-1</v>
@@ -3394,15 +3394,15 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B97">
         <v>40</v>
@@ -3411,18 +3411,18 @@
         <v>200</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B98">
         <v>20</v>
@@ -3431,18 +3431,18 @@
         <v>40</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3451,18 +3451,18 @@
         <v>20</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="E99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100">
         <v>-1</v>
@@ -3474,15 +3474,15 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
+        <v>130</v>
+      </c>
+      <c r="F100" t="s">
         <v>131</v>
-      </c>
-      <c r="F100" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B101">
         <v>-2</v>
@@ -3494,15 +3494,15 @@
         <v>15</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B102">
         <v>30</v>
@@ -3511,18 +3511,18 @@
         <v>200</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F102" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B103">
         <v>15</v>
@@ -3531,18 +3531,18 @@
         <v>30</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E103" t="s">
         <v>136</v>
       </c>
-      <c r="E103" t="s">
-        <v>137</v>
-      </c>
       <c r="F103" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3551,18 +3551,18 @@
         <v>15</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B105">
         <v>-1</v>
@@ -3574,15 +3574,15 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B106">
         <v>-2</v>
@@ -3594,15 +3594,15 @@
         <v>15</v>
       </c>
       <c r="E106" t="s">
+        <v>138</v>
+      </c>
+      <c r="F106" t="s">
         <v>139</v>
-      </c>
-      <c r="F106" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B107">
         <v>90</v>
@@ -3611,18 +3611,18 @@
         <v>200</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B108">
         <v>60</v>
@@ -3631,18 +3631,18 @@
         <v>90</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E108" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F108" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B109">
         <v>30</v>
@@ -3654,15 +3654,15 @@
         <v>57</v>
       </c>
       <c r="E109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B110">
         <v>15</v>
@@ -3671,18 +3671,18 @@
         <v>30</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E110" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3691,18 +3691,18 @@
         <v>15</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B112">
         <v>-1</v>
@@ -3714,15 +3714,15 @@
         <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B113">
         <v>-2</v>
@@ -3734,15 +3734,15 @@
         <v>15</v>
       </c>
       <c r="E113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B114">
         <v>80</v>
@@ -3751,18 +3751,18 @@
         <v>200</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E114" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F114" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B115">
         <v>60</v>
@@ -3771,18 +3771,18 @@
         <v>80</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E115" t="s">
         <v>146</v>
       </c>
-      <c r="E115" t="s">
-        <v>147</v>
-      </c>
       <c r="F115" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B116">
         <v>40</v>
@@ -3791,18 +3791,18 @@
         <v>60</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E116" t="s">
         <v>148</v>
       </c>
-      <c r="E116" t="s">
-        <v>149</v>
-      </c>
       <c r="F116" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117">
         <v>30</v>
@@ -3811,18 +3811,18 @@
         <v>40</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E117" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B118">
         <v>20</v>
@@ -3831,18 +3831,18 @@
         <v>30</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B119">
         <v>10</v>
@@ -3851,18 +3851,18 @@
         <v>20</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3874,15 +3874,15 @@
         <v>13</v>
       </c>
       <c r="E120" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B121">
         <v>-1</v>
@@ -3894,15 +3894,15 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F121" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B122">
         <v>80</v>
@@ -3911,18 +3911,18 @@
         <v>200</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E122" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B123">
         <v>60</v>
@@ -3931,18 +3931,18 @@
         <v>80</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F123" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B124">
         <v>40</v>
@@ -3951,18 +3951,18 @@
         <v>60</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F124" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B125">
         <v>30</v>
@@ -3971,18 +3971,18 @@
         <v>40</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B126">
         <v>20</v>
@@ -3991,18 +3991,18 @@
         <v>30</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E126" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F126" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B127">
         <v>10</v>
@@ -4011,18 +4011,18 @@
         <v>20</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F127" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -4034,15 +4034,15 @@
         <v>13</v>
       </c>
       <c r="E128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F128" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B129">
         <v>-1</v>
@@ -4054,15 +4054,15 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F129" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B130">
         <v>30</v>
@@ -4071,18 +4071,18 @@
         <v>200</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E130" t="s">
+        <v>168</v>
+      </c>
+      <c r="F130" t="s">
         <v>169</v>
-      </c>
-      <c r="F130" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B131">
         <v>5</v>
@@ -4091,18 +4091,18 @@
         <v>30</v>
       </c>
       <c r="D131" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E131" t="s">
         <v>171</v>
       </c>
-      <c r="E131" t="s">
-        <v>172</v>
-      </c>
       <c r="F131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B132">
         <v>-1</v>
@@ -4114,15 +4114,15 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F132" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B133">
         <v>-2</v>
@@ -4134,15 +4134,15 @@
         <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F133" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B134">
         <v>50</v>
@@ -4151,18 +4151,18 @@
         <v>200</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" t="s">
         <v>176</v>
       </c>
-      <c r="E134" t="s">
-        <v>177</v>
-      </c>
       <c r="F134" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B135">
         <v>20</v>
@@ -4171,18 +4171,18 @@
         <v>50</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -4191,18 +4191,18 @@
         <v>20</v>
       </c>
       <c r="D136" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E136" t="s">
         <v>180</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>181</v>
-      </c>
-      <c r="F136" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B137">
         <v>-1</v>
@@ -4214,15 +4214,15 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
+        <v>180</v>
+      </c>
+      <c r="F137" t="s">
         <v>181</v>
-      </c>
-      <c r="F137" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B138">
         <v>-2</v>
@@ -4234,15 +4234,15 @@
         <v>15</v>
       </c>
       <c r="E138" t="s">
+        <v>180</v>
+      </c>
+      <c r="F138" t="s">
         <v>181</v>
-      </c>
-      <c r="F138" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B139">
         <v>-2</v>
@@ -4251,18 +4251,18 @@
         <v>200</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E139" t="s">
+        <v>183</v>
+      </c>
+      <c r="F139" t="s">
         <v>184</v>
-      </c>
-      <c r="F139" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B140">
         <v>80</v>
@@ -4271,18 +4271,18 @@
         <v>200</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E140" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B141">
         <v>30</v>
@@ -4291,18 +4291,18 @@
         <v>80</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E141" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F141" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4311,18 +4311,18 @@
         <v>30</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E142" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B143">
         <v>-1</v>
@@ -4334,35 +4334,35 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144">
+        <v>-2</v>
+      </c>
+      <c r="C144">
+        <v>-2</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E144" t="s">
+        <v>245</v>
+      </c>
+      <c r="F144" t="s">
         <v>164</v>
-      </c>
-      <c r="B144">
-        <v>-2</v>
-      </c>
-      <c r="C144">
-        <v>-2</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E144" t="s">
-        <v>246</v>
-      </c>
-      <c r="F144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B145">
         <v>100</v>
@@ -4371,18 +4371,18 @@
         <v>200</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E145" t="s">
+        <v>186</v>
+      </c>
+      <c r="F145" t="s">
         <v>187</v>
-      </c>
-      <c r="F145" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B146">
         <v>50</v>
@@ -4391,18 +4391,18 @@
         <v>100</v>
       </c>
       <c r="D146" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" t="s">
         <v>190</v>
       </c>
-      <c r="E146" t="s">
-        <v>191</v>
-      </c>
       <c r="F146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B147">
         <v>20</v>
@@ -4411,18 +4411,18 @@
         <v>50</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E147" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F147" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4431,18 +4431,18 @@
         <v>20</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B149">
         <v>-1</v>
@@ -4454,15 +4454,15 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F149" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B150">
         <v>-2</v>
@@ -4471,18 +4471,18 @@
         <v>-2</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E150" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F150" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B151">
         <v>-2</v>
@@ -4491,18 +4491,18 @@
         <v>200</v>
       </c>
       <c r="D151" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E151" t="s">
         <v>195</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>196</v>
-      </c>
-      <c r="F151" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B152">
         <v>-2</v>
@@ -4511,18 +4511,18 @@
         <v>200</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E152" t="s">
+        <v>198</v>
+      </c>
+      <c r="F152" t="s">
         <v>199</v>
-      </c>
-      <c r="F152" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B153">
         <v>-2</v>
@@ -4531,18 +4531,18 @@
         <v>200</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E153" t="s">
+        <v>201</v>
+      </c>
+      <c r="F153" t="s">
         <v>202</v>
-      </c>
-      <c r="F153" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B154">
         <v>10</v>
@@ -4551,18 +4551,18 @@
         <v>200</v>
       </c>
       <c r="D154" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E154" t="s">
+        <v>203</v>
+      </c>
+      <c r="F154" t="s">
         <v>208</v>
-      </c>
-      <c r="E154" t="s">
-        <v>204</v>
-      </c>
-      <c r="F154" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4574,15 +4574,15 @@
         <v>13</v>
       </c>
       <c r="E155" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F155" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B156">
         <v>-1</v>
@@ -4594,15 +4594,15 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F156" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B157">
         <v>-2</v>
@@ -4611,18 +4611,18 @@
         <v>-2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F157" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B158">
         <v>90</v>
@@ -4631,18 +4631,18 @@
         <v>200</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E158" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F158" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B159">
         <v>80</v>
@@ -4651,18 +4651,18 @@
         <v>90</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E159" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F159" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B160">
         <v>70</v>
@@ -4671,18 +4671,18 @@
         <v>80</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E160" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F160" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B161">
         <v>60</v>
@@ -4691,18 +4691,18 @@
         <v>70</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E161" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F161" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B162">
         <v>50</v>
@@ -4711,18 +4711,18 @@
         <v>60</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E162" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F162" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B163">
         <v>40</v>
@@ -4731,18 +4731,18 @@
         <v>50</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E163" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F163" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B164">
         <v>30</v>
@@ -4751,18 +4751,18 @@
         <v>40</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E164" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F164" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B165">
         <v>20</v>
@@ -4771,18 +4771,18 @@
         <v>30</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E165" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F165" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B166">
         <v>10</v>
@@ -4791,18 +4791,18 @@
         <v>20</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E166" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F166" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B167">
         <v>5</v>
@@ -4811,18 +4811,18 @@
         <v>10</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E167" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F167" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4831,18 +4831,18 @@
         <v>5</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E168" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F168" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B169">
         <v>-1</v>
@@ -4854,10 +4854,10 @@
         <v>14</v>
       </c>
       <c r="E169" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F169" t="s">
         <v>223</v>
-      </c>
-      <c r="F169" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>
